--- a/priceUpdate/trade_agreement_templates/LIST Trade Agreement.xlsx
+++ b/priceUpdate/trade_agreement_templates/LIST Trade Agreement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://reliablesprinkler-my.sharepoint.com/personal/btrent_reliablesprinkler_com/Documents/Documents/GitHub/reliable-PIM/priceUpdate/trade_agreement_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1057" documentId="8_{F69A5B1D-35AF-4916-A00F-77A7DAB05B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D8857EE-5A98-4EF0-8FB3-FC7E3FEC5AC7}"/>
+  <xr:revisionPtr revIDLastSave="1079" documentId="8_{F69A5B1D-35AF-4916-A00F-77A7DAB05B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58482EF8-6C0C-44B9-9422-AFA1D75EA6CA}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1365" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="368" yWindow="368" windowWidth="16199" windowHeight="10035" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -680,7 +680,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="1" width="350" row="6">
+  <wetp:taskpane dockstate="right" visibility="1" width="700" row="7">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -699,24 +699,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="1"/>
     <col min="2" max="2" width="19" style="1"/>
     <col min="3" max="4" width="21" style="1"/>
     <col min="5" max="5" width="17" style="1"/>
     <col min="6" max="6" width="8" style="2"/>
-    <col min="7" max="7" width="12.42578125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.3984375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.1328125" style="1" customWidth="1"/>
     <col min="9" max="9" width="22" style="2"/>
     <col min="10" max="10" width="12" style="1"/>
     <col min="11" max="11" width="13" style="3"/>
     <col min="12" max="12" width="18" style="9"/>
     <col min="13" max="13" width="14" style="6"/>
-    <col min="14" max="14" width="21.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.59765625" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -760,7 +760,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -771,7 +771,7 @@
         <v>12</v>
       </c>
       <c r="E2" s="8">
-        <v>6990031201</v>
+        <v>6990031218</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
@@ -781,10 +781,10 @@
       </c>
       <c r="K2" s="5">
         <f t="shared" ref="K2" ca="1" si="0">TODAY()</f>
-        <v>46269</v>
+        <v>46275</v>
       </c>
       <c r="L2" s="10">
-        <v>5000</v>
+        <v>40000</v>
       </c>
       <c r="M2" s="6">
         <v>1</v>
@@ -808,42 +808,42 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B7E878A-1B87-4CC1-AE38-60BDEDA0007E}">
   <dimension ref="F3:F9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="6" max="6" width="15.140625" customWidth="1"/>
+    <col min="6" max="6" width="15.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="6:6" x14ac:dyDescent="0.45">
       <c r="F3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="6:6" x14ac:dyDescent="0.45">
       <c r="F4">
         <v>6990031149</v>
       </c>
     </row>
-    <row r="5" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="6:6" x14ac:dyDescent="0.45">
       <c r="F5">
         <v>6990031150</v>
       </c>
     </row>
-    <row r="6" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="6:6" x14ac:dyDescent="0.45">
       <c r="F6">
         <v>6990031151</v>
       </c>
     </row>
-    <row r="7" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="6:6" x14ac:dyDescent="0.45">
       <c r="F7">
         <v>6990031152</v>
       </c>
     </row>
-    <row r="8" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="6:6" x14ac:dyDescent="0.45">
       <c r="F8">
         <v>6990031153</v>
       </c>
     </row>
-    <row r="9" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="6:6" x14ac:dyDescent="0.45">
       <c r="F9">
         <v>6990031154</v>
       </c>
@@ -859,14 +859,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55B2EDAD-2FEB-49CE-8DFA-E15AFB09D81B}">
   <dimension ref="B6:D24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="20.28515625" customWidth="1"/>
-    <col min="3" max="3" width="25.42578125" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.265625" customWidth="1"/>
+    <col min="3" max="3" width="25.3984375" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>18</v>
       </c>
@@ -874,7 +874,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>20</v>
       </c>
@@ -885,7 +885,7 @@
         <v>8300</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>22</v>
       </c>
@@ -896,7 +896,7 @@
         <v>8300</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>24</v>
       </c>
@@ -907,7 +907,7 @@
         <v>8300</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>26</v>
       </c>
@@ -918,7 +918,7 @@
         <v>8300</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>28</v>
       </c>
@@ -929,7 +929,7 @@
         <v>8300</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>30</v>
       </c>
@@ -940,7 +940,7 @@
         <v>8300</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>32</v>
       </c>
@@ -951,7 +951,7 @@
         <v>8300</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>34</v>
       </c>
@@ -962,22 +962,22 @@
         <v>8300</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.45">
       <c r="D16" s="7" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.45">
       <c r="D17" s="7" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.45">
       <c r="D18" s="7" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
         <v>36</v>
       </c>
@@ -985,12 +985,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.45">
       <c r="D20" s="7" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
         <v>37</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
         <v>39</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
         <v>41</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
         <v>43</v>
       </c>
